--- a/src/main/resources/input/KING/props/KING.xlsx
+++ b/src/main/resources/input/KING/props/KING.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\gitprojects\Imvertor-Maven\src\main\resources\input\KING\props\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\github.com\Imvertor-Maven\src\main\resources\input\KING\props\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD7C644-2A6D-4F70-AF1A-663D66856F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB5AC0F-B5C4-4D0A-83FD-81B31C20F5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="2280" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5610" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KING" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="437">
   <si>
     <t>Name</t>
   </si>
@@ -1356,6 +1356,12 @@
   </si>
   <si>
     <t>MBG</t>
+  </si>
+  <si>
+    <t>officeexpansion</t>
+  </si>
+  <si>
+    <t>Yes if inherited attributes and relations are to be grouped by supertype and  indicated as inherited in Respec documentation.</t>
   </si>
 </sst>
 </file>
@@ -1957,36 +1963,36 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z158"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Z159"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.84375" customWidth="1"/>
-    <col min="2" max="2" width="20.15234375" customWidth="1"/>
-    <col min="3" max="3" width="50.69140625" customWidth="1"/>
-    <col min="4" max="4" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" customWidth="1"/>
+    <col min="3" max="3" width="50.7265625" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="15" customWidth="1"/>
-    <col min="8" max="8" width="16.61328125" customWidth="1"/>
-    <col min="9" max="9" width="14.69140625" customWidth="1"/>
-    <col min="10" max="10" width="14.23046875" customWidth="1"/>
-    <col min="11" max="11" width="15.69140625" customWidth="1"/>
-    <col min="12" max="12" width="12.69140625" customWidth="1"/>
-    <col min="13" max="13" width="2.3828125" style="15" customWidth="1"/>
-    <col min="14" max="14" width="18.69140625" customWidth="1"/>
-    <col min="15" max="15" width="16.07421875" customWidth="1"/>
-    <col min="16" max="17" width="15.69140625" customWidth="1"/>
-    <col min="18" max="18" width="12.921875" customWidth="1"/>
-    <col min="19" max="19" width="2.3828125" style="15" customWidth="1"/>
-    <col min="20" max="20" width="19.921875" customWidth="1"/>
-    <col min="21" max="21" width="19.61328125" customWidth="1"/>
+    <col min="7" max="7" width="2.7265625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="16.6328125" customWidth="1"/>
+    <col min="9" max="9" width="14.7265625" customWidth="1"/>
+    <col min="10" max="10" width="14.26953125" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="13" max="13" width="2.36328125" style="15" customWidth="1"/>
+    <col min="14" max="14" width="18.7265625" customWidth="1"/>
+    <col min="15" max="15" width="16.08984375" customWidth="1"/>
+    <col min="16" max="17" width="15.7265625" customWidth="1"/>
+    <col min="18" max="18" width="12.90625" customWidth="1"/>
+    <col min="19" max="19" width="2.36328125" style="15" customWidth="1"/>
+    <col min="20" max="20" width="19.90625" customWidth="1"/>
+    <col min="21" max="21" width="19.6328125" customWidth="1"/>
     <col min="22" max="23" width="18" customWidth="1"/>
-    <col min="24" max="24" width="19.61328125" customWidth="1"/>
-    <col min="25" max="25" width="63.61328125" customWidth="1"/>
-    <col min="26" max="26" width="30.07421875" customWidth="1"/>
+    <col min="24" max="24" width="19.6328125" customWidth="1"/>
+    <col min="25" max="25" width="63.6328125" customWidth="1"/>
+    <col min="26" max="26" width="30.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="3" customFormat="1" ht="37.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:26" s="3" customFormat="1" ht="56.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2057,7 +2063,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="3" customFormat="1" ht="56.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:26" s="3" customFormat="1" ht="56.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="F2" s="31"/>
       <c r="G2" s="11"/>
       <c r="H2" s="2" t="s">
@@ -2108,7 +2114,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="1" customFormat="1" ht="29.6" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:26" s="1" customFormat="1" ht="44" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>150</v>
       </c>
@@ -2129,7 +2135,7 @@
       <c r="M3" s="12"/>
       <c r="S3" s="12"/>
     </row>
-    <row r="4" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2152,7 +2158,7 @@
       <c r="M4" s="12"/>
       <c r="S4" s="12"/>
     </row>
-    <row r="5" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2175,7 +2181,7 @@
       <c r="M5" s="12"/>
       <c r="S5" s="12"/>
     </row>
-    <row r="6" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>153</v>
       </c>
@@ -2196,7 +2202,7 @@
       <c r="M6" s="12"/>
       <c r="S6" s="12"/>
     </row>
-    <row r="7" spans="1:26" s="1" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="43" t="s">
         <v>9</v>
       </c>
@@ -2223,7 +2229,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="43"/>
       <c r="B8" s="43"/>
       <c r="C8" s="43"/>
@@ -2234,7 +2240,7 @@
       <c r="S8" s="12"/>
       <c r="Y8" s="42"/>
     </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:26" s="4" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>156</v>
       </c>
@@ -2263,7 +2269,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -2286,7 +2292,7 @@
       <c r="M10" s="12"/>
       <c r="S10" s="12"/>
     </row>
-    <row r="11" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>158</v>
       </c>
@@ -2307,7 +2313,7 @@
       <c r="M11" s="12"/>
       <c r="S11" s="12"/>
     </row>
-    <row r="12" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>131</v>
       </c>
@@ -2328,7 +2334,7 @@
       <c r="M12" s="12"/>
       <c r="S12" s="12"/>
     </row>
-    <row r="13" spans="1:26" s="1" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>234</v>
       </c>
@@ -2355,7 +2361,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:26" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -2378,7 +2384,7 @@
       <c r="M14" s="12"/>
       <c r="S14" s="12"/>
     </row>
-    <row r="15" spans="1:26" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:26" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -2407,7 +2413,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="16" spans="1:26" s="1" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:26" s="1" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -2433,7 +2439,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="17" spans="1:26" s="1" customFormat="1" ht="17.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:26" s="1" customFormat="1" ht="17.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>212</v>
       </c>
@@ -2456,7 +2462,7 @@
       <c r="M17" s="12"/>
       <c r="S17" s="12"/>
     </row>
-    <row r="18" spans="1:26" s="1" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:26" s="1" customFormat="1" ht="156.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>214</v>
       </c>
@@ -2530,7 +2536,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="19" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>160</v>
       </c>
@@ -2553,7 +2559,7 @@
       <c r="M19" s="12"/>
       <c r="S19" s="12"/>
     </row>
-    <row r="20" spans="1:26" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:26" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>133</v>
       </c>
@@ -2579,7 +2585,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="21" spans="1:26" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:26" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>136</v>
       </c>
@@ -2605,7 +2611,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="22" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>139</v>
       </c>
@@ -2634,7 +2640,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="23" spans="1:26" s="4" customFormat="1" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:26" s="4" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2667,7 +2673,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="24" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>162</v>
       </c>
@@ -2688,7 +2694,7 @@
       <c r="M24" s="12"/>
       <c r="S24" s="12"/>
     </row>
-    <row r="25" spans="1:26" s="1" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -2717,7 +2723,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="26" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -2761,7 +2767,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="27" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>410</v>
       </c>
@@ -2805,7 +2811,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="28" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
@@ -2831,7 +2837,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="29" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>141</v>
       </c>
@@ -2857,7 +2863,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="30" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>285</v>
       </c>
@@ -2881,7 +2887,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="31" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>247</v>
       </c>
@@ -2905,7 +2911,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="32" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>252</v>
       </c>
@@ -2933,7 +2939,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="33" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
@@ -2971,7 +2977,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="34" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>164</v>
       </c>
@@ -2997,7 +3003,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="35" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>167</v>
       </c>
@@ -3021,7 +3027,7 @@
       <c r="S35" s="12"/>
       <c r="Y35" s="22"/>
     </row>
-    <row r="36" spans="1:26" s="1" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>257</v>
       </c>
@@ -3047,7 +3053,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="37" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>37</v>
       </c>
@@ -3068,7 +3074,7 @@
       <c r="M37" s="12"/>
       <c r="S37" s="12"/>
     </row>
-    <row r="38" spans="1:26" s="17" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:26" s="17" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>269</v>
       </c>
@@ -3094,7 +3100,7 @@
       </c>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" s="1" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
@@ -3117,7 +3123,7 @@
       <c r="M39" s="12"/>
       <c r="S39" s="12"/>
     </row>
-    <row r="40" spans="1:26" s="1" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -3146,7 +3152,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="41" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>43</v>
       </c>
@@ -3169,7 +3175,7 @@
       <c r="M41" s="12"/>
       <c r="S41" s="12"/>
     </row>
-    <row r="42" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>251</v>
       </c>
@@ -3192,7 +3198,7 @@
       <c r="M42" s="33"/>
       <c r="S42" s="33"/>
     </row>
-    <row r="43" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>170</v>
       </c>
@@ -3230,7 +3236,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="44" spans="1:26" s="4" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:26" s="4" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A44" s="17" t="s">
         <v>45</v>
       </c>
@@ -3267,7 +3273,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="45" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="43" t="s">
         <v>47</v>
       </c>
@@ -3296,7 +3302,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="46" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="43"/>
       <c r="B46" s="43"/>
       <c r="C46" s="43"/>
@@ -3307,7 +3313,7 @@
       <c r="S46" s="12"/>
       <c r="Y46" s="42"/>
     </row>
-    <row r="47" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>172</v>
       </c>
@@ -3328,7 +3334,7 @@
       <c r="M47" s="12"/>
       <c r="S47" s="12"/>
     </row>
-    <row r="48" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
@@ -3351,7 +3357,7 @@
       <c r="M48" s="12"/>
       <c r="S48" s="12"/>
     </row>
-    <row r="49" spans="1:26" s="1" customFormat="1" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:26" s="1" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -3380,7 +3386,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="50" spans="1:26" s="1" customFormat="1" ht="160.30000000000001" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:26" s="1" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>210</v>
       </c>
@@ -3407,7 +3413,7 @@
       </c>
       <c r="Z50"/>
     </row>
-    <row r="51" spans="1:26" s="4" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:26" s="4" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="17" t="s">
         <v>175</v>
       </c>
@@ -3433,7 +3439,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="52" spans="1:26" s="4" customFormat="1" ht="86.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:26" s="4" customFormat="1" ht="86.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="17" t="s">
         <v>177</v>
       </c>
@@ -3472,7 +3478,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="53" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>54</v>
       </c>
@@ -3494,7 +3500,7 @@
       <c r="S53" s="12"/>
       <c r="Y53" s="22"/>
     </row>
-    <row r="54" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>56</v>
       </c>
@@ -3521,7 +3527,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="55" spans="1:26" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:26" s="4" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>58</v>
       </c>
@@ -3553,7 +3559,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="56" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>180</v>
       </c>
@@ -3577,7 +3583,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" s="37" t="s">
         <v>275</v>
       </c>
@@ -3614,7 +3620,7 @@
       </c>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>277</v>
       </c>
@@ -3639,7 +3645,7 @@
       </c>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>182</v>
       </c>
@@ -3662,7 +3668,7 @@
       <c r="Y59" s="22"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>280</v>
       </c>
@@ -3697,7 +3703,7 @@
       </c>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:26" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
         <v>230</v>
       </c>
@@ -3739,7 +3745,7 @@
       </c>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" s="4" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:26" s="4" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>184</v>
       </c>
@@ -3765,7 +3771,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="63" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>60</v>
       </c>
@@ -3789,7 +3795,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="64" spans="1:26" s="1" customFormat="1" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:26" s="1" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>291</v>
       </c>
@@ -3816,7 +3822,7 @@
       </c>
       <c r="Z64" s="33"/>
     </row>
-    <row r="65" spans="1:26" s="4" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:26" s="4" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>62</v>
       </c>
@@ -3842,7 +3848,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="66" spans="1:26" s="4" customFormat="1" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:26" s="4" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>293</v>
       </c>
@@ -3863,7 +3869,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="67" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="37" t="s">
         <v>249</v>
       </c>
@@ -3887,7 +3893,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="68" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>65</v>
       </c>
@@ -3910,7 +3916,7 @@
       <c r="M68" s="12"/>
       <c r="S68" s="12"/>
     </row>
-    <row r="69" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
@@ -3933,7 +3939,7 @@
       <c r="M69" s="12"/>
       <c r="S69" s="12"/>
     </row>
-    <row r="70" spans="1:26" s="1" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>241</v>
       </c>
@@ -3962,7 +3968,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="71" spans="1:26" s="1" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>186</v>
       </c>
@@ -3988,7 +3994,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="72" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>69</v>
       </c>
@@ -4011,7 +4017,7 @@
       <c r="M72" s="12"/>
       <c r="S72" s="12"/>
     </row>
-    <row r="73" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>423</v>
       </c>
@@ -4077,7 +4083,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="74" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>426</v>
       </c>
@@ -4143,7 +4149,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="75" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>428</v>
       </c>
@@ -4209,7 +4215,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="76" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>430</v>
       </c>
@@ -4231,7 +4237,7 @@
       <c r="S76" s="12"/>
       <c r="T76"/>
     </row>
-    <row r="77" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>189</v>
       </c>
@@ -4252,7 +4258,7 @@
       <c r="M77" s="12"/>
       <c r="S77" s="12"/>
     </row>
-    <row r="78" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A78" s="17" t="s">
         <v>71</v>
       </c>
@@ -4287,7 +4293,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="79" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="17" t="s">
         <v>413</v>
       </c>
@@ -4318,7 +4324,7 @@
       <c r="Y79" s="21"/>
       <c r="Z79" s="12"/>
     </row>
-    <row r="80" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>208</v>
       </c>
@@ -4341,7 +4347,7 @@
       <c r="M80" s="12"/>
       <c r="S80" s="12"/>
     </row>
-    <row r="81" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>73</v>
       </c>
@@ -4370,7 +4376,7 @@
       <c r="U81" s="17"/>
       <c r="X81" s="17"/>
     </row>
-    <row r="82" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>75</v>
       </c>
@@ -4396,7 +4402,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="83" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>77</v>
       </c>
@@ -4419,122 +4425,122 @@
       <c r="M83" s="12"/>
       <c r="S83" s="12"/>
     </row>
-    <row r="84" spans="1:26" s="4" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A84" s="4" t="s">
+    <row r="84" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D84" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="G84" s="12"/>
+      <c r="M84" s="12"/>
+      <c r="S84" s="12"/>
+    </row>
+    <row r="85" spans="1:26" s="4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B85" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C85" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D84" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F84" s="27" t="s">
+      <c r="D85" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" s="27" t="s">
         <v>296</v>
       </c>
-      <c r="G84" s="12"/>
-      <c r="H84" s="17"/>
-      <c r="M84" s="12"/>
-      <c r="N84" s="17"/>
-      <c r="O84" s="17"/>
-      <c r="R84" s="17"/>
-      <c r="S84" s="12"/>
-      <c r="U84" s="17"/>
-      <c r="X84" s="17"/>
-      <c r="Y84" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="Z84" s="4" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="85" spans="1:26" s="4" customFormat="1" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A85" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D85" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" s="27"/>
       <c r="G85" s="12"/>
       <c r="H85" s="17"/>
       <c r="M85" s="12"/>
+      <c r="N85" s="17"/>
+      <c r="O85" s="17"/>
+      <c r="R85" s="17"/>
       <c r="S85" s="12"/>
-      <c r="Y85" s="22" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="86" spans="1:26" s="1" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A86" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D86" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E86" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F86" s="26" t="s">
-        <v>19</v>
-      </c>
+      <c r="U85" s="17"/>
+      <c r="X85" s="17"/>
+      <c r="Y85" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="Z85" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="86" spans="1:26" s="4" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D86" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="27"/>
       <c r="G86" s="12"/>
+      <c r="H86" s="17"/>
       <c r="M86" s="12"/>
       <c r="S86" s="12"/>
       <c r="Y86" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="Z86" s="4"/>
-    </row>
-    <row r="87" spans="1:26" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A87" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D87" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E87" s="4"/>
-      <c r="F87" s="27"/>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="87" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D87" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E87" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" s="26" t="s">
+        <v>19</v>
+      </c>
       <c r="G87" s="12"/>
       <c r="M87" s="12"/>
       <c r="S87" s="12"/>
       <c r="Y87" s="22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="Z87" s="4"/>
     </row>
-    <row r="88" spans="1:26" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:26" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D88" s="4" t="b">
         <v>0</v>
@@ -4549,15 +4555,15 @@
       </c>
       <c r="Z88" s="4"/>
     </row>
-    <row r="89" spans="1:26" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:26" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D89" s="4" t="b">
         <v>0</v>
@@ -4572,12 +4578,12 @@
       </c>
       <c r="Z89" s="4"/>
     </row>
-    <row r="90" spans="1:26" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:26" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>307</v>
@@ -4595,290 +4601,284 @@
       </c>
       <c r="Z90" s="4"/>
     </row>
-    <row r="91" spans="1:26" s="4" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:26" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>193</v>
+        <v>308</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>173</v>
+        <v>309</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>194</v>
+        <v>307</v>
       </c>
       <c r="D91" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E91" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F91" s="27" t="s">
-        <v>203</v>
-      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="27"/>
       <c r="G91" s="12"/>
       <c r="M91" s="12"/>
       <c r="S91" s="12"/>
       <c r="Y91" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="Z91" s="4"/>
+    </row>
+    <row r="92" spans="1:26" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D92" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F92" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="G92" s="12"/>
+      <c r="M92" s="12"/>
+      <c r="S92" s="12"/>
+      <c r="Y92" s="22" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="92" spans="1:26" s="1" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A92" s="1" t="s">
+    <row r="93" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D92" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F92" s="26" t="s">
+      <c r="D93" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F93" s="26" t="s">
         <v>399</v>
       </c>
-      <c r="G92" s="12"/>
-      <c r="H92" s="1" t="s">
+      <c r="G93" s="12"/>
+      <c r="H93" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I92" s="1" t="s">
+      <c r="I93" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="J92" s="1" t="s">
+      <c r="J93" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K92" s="1" t="s">
+      <c r="K93" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="L92" s="1" t="s">
+      <c r="L93" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="M92" s="12"/>
-      <c r="N92" s="1" t="s">
+      <c r="M93" s="12"/>
+      <c r="N93" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="O92" s="1" t="s">
+      <c r="O93" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="P92" s="1" t="s">
+      <c r="P93" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="Q92" s="1" t="s">
+      <c r="Q93" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="R92" s="1" t="s">
+      <c r="R93" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="S92" s="12"/>
-      <c r="T92" s="1" t="s">
+      <c r="S93" s="12"/>
+      <c r="T93" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="U92" s="1" t="s">
+      <c r="U93" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="V92" s="1" t="s">
+      <c r="V93" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="W92" s="1" t="s">
+      <c r="W93" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="X92" s="1" t="s">
+      <c r="X93" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="Y92" s="22" t="s">
+      <c r="Y93" s="22" t="s">
         <v>394</v>
       </c>
-      <c r="Z92" s="1" t="s">
+      <c r="Z93" s="1" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="93" spans="1:26" s="1" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A93" s="1" t="s">
+    <row r="94" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D93" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F93" s="26" t="s">
+      <c r="D94" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F94" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="G93" s="12"/>
-      <c r="M93" s="12"/>
-      <c r="S93" s="12"/>
-      <c r="Y93" s="22" t="s">
+      <c r="G94" s="12"/>
+      <c r="M94" s="12"/>
+      <c r="S94" s="12"/>
+      <c r="Y94" s="22" t="s">
         <v>340</v>
       </c>
-      <c r="Z93" s="1" t="s">
+      <c r="Z94" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="94" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A94" s="4" t="s">
+    <row r="95" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B95" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C95" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D94" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E94" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F94" s="27" t="s">
+      <c r="D95" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E95" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="G94" s="12"/>
-      <c r="H94" s="1"/>
-      <c r="M94" s="12"/>
-      <c r="N94" s="1"/>
-      <c r="O94" s="1"/>
-      <c r="R94" s="1"/>
-      <c r="S94" s="12"/>
-      <c r="U94" s="1"/>
-      <c r="X94" s="1"/>
-      <c r="Y94" s="21" t="s">
+      <c r="G95" s="12"/>
+      <c r="H95" s="1"/>
+      <c r="M95" s="12"/>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1"/>
+      <c r="R95" s="1"/>
+      <c r="S95" s="12"/>
+      <c r="U95" s="1"/>
+      <c r="X95" s="1"/>
+      <c r="Y95" s="21" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="95" spans="1:26" s="4" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="4" t="s">
+    <row r="96" spans="1:26" s="4" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B96" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C96" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D95" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E95" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F95" s="27" t="s">
+      <c r="D96" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F96" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="S95" s="12"/>
-      <c r="Y95" s="22" t="s">
+      <c r="G96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="S96" s="12"/>
+      <c r="Y96" s="22" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="96" spans="1:26" s="4" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="17" t="s">
+    <row r="97" spans="1:26" s="4" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="17" t="s">
         <v>418</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B97" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C96" s="17" t="s">
+      <c r="C97" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="D96" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="E96" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F96" s="17" t="s">
+      <c r="D97" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F97" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G96" s="12"/>
-      <c r="L96" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="12"/>
-      <c r="R96" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="S96" s="12"/>
-      <c r="X96" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y96" s="22"/>
-    </row>
-    <row r="97" spans="1:26" s="1" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A97" s="1" t="s">
+      <c r="G97" s="12"/>
+      <c r="L97" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M97" s="12"/>
+      <c r="R97" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="S97" s="12"/>
+      <c r="X97" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y97" s="22"/>
+    </row>
+    <row r="98" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A98" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B98" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D97" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E97" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F97" s="26" t="s">
+      <c r="D98" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" s="26" t="s">
         <v>93</v>
-      </c>
-      <c r="G97" s="12"/>
-      <c r="M97" s="12"/>
-      <c r="S97" s="12"/>
-    </row>
-    <row r="98" spans="1:26" s="1" customFormat="1" ht="102" x14ac:dyDescent="0.4">
-      <c r="A98" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="B98" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C98" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="D98" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F98" s="26" t="s">
-        <v>4</v>
       </c>
       <c r="G98" s="12"/>
       <c r="M98" s="12"/>
       <c r="S98" s="12"/>
-      <c r="Y98" s="22" t="s">
-        <v>395</v>
-      </c>
-      <c r="Z98" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="99" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="99" spans="1:26" s="1" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A99" s="32" t="s">
-        <v>215</v>
+        <v>310</v>
       </c>
       <c r="B99" s="32" t="s">
         <v>5</v>
       </c>
       <c r="C99" s="32" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D99" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" s="32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" s="26" t="s">
         <v>4</v>
@@ -4886,24 +4886,27 @@
       <c r="G99" s="12"/>
       <c r="M99" s="12"/>
       <c r="S99" s="12"/>
-      <c r="Z99" s="12" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="100" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A100" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B100" s="1" t="s">
+      <c r="Y99" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="Z99" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" s="1" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A100" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="B100" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D100" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E100" s="1" t="b">
+      <c r="C100" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="D100" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" s="32" t="b">
         <v>1</v>
       </c>
       <c r="F100" s="26" t="s">
@@ -4912,77 +4915,77 @@
       <c r="G100" s="12"/>
       <c r="M100" s="12"/>
       <c r="S100" s="12"/>
-      <c r="Y100" s="22" t="s">
-        <v>327</v>
-      </c>
-      <c r="Z100" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="101" spans="1:26" s="1" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
+      <c r="Z100" s="12" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="D101" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>255</v>
+        <v>4</v>
       </c>
       <c r="G101" s="12"/>
       <c r="M101" s="12"/>
       <c r="S101" s="12"/>
       <c r="Y101" s="22" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="Z101" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="102" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A102" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D102" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E102" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F102" s="27" t="s">
-        <v>400</v>
+        <v>382</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A102" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D102" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>255</v>
       </c>
       <c r="G102" s="12"/>
       <c r="M102" s="12"/>
       <c r="S102" s="12"/>
       <c r="Y102" s="22" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="103" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+        <v>396</v>
+      </c>
+      <c r="Z102" s="1" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="D103" s="4" t="b">
         <v>0</v>
@@ -4990,7 +4993,9 @@
       <c r="E103" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F103" s="39"/>
+      <c r="F103" s="27" t="s">
+        <v>400</v>
+      </c>
       <c r="G103" s="12"/>
       <c r="M103" s="12"/>
       <c r="S103" s="12"/>
@@ -4998,169 +5003,170 @@
         <v>327</v>
       </c>
     </row>
-    <row r="104" spans="1:26" s="1" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>10</v>
+        <v>238</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>313</v>
+        <v>239</v>
       </c>
       <c r="D104" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="F104" s="27" t="s">
-        <v>209</v>
-      </c>
+      <c r="F104" s="39"/>
       <c r="G104" s="12"/>
       <c r="M104" s="12"/>
       <c r="S104" s="12"/>
       <c r="Y104" s="22" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="105" spans="1:26" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D105" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E105" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F105" s="26" t="s">
-        <v>16</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A105" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D105" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F105" s="27" t="s">
+        <v>209</v>
       </c>
       <c r="G105" s="12"/>
       <c r="M105" s="12"/>
       <c r="S105" s="12"/>
-    </row>
-    <row r="106" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D106" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E106" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F106" s="35" t="s">
-        <v>209</v>
+      <c r="Y105" s="22" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D106" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" s="26" t="s">
+        <v>16</v>
       </c>
       <c r="G106" s="12"/>
-      <c r="H106" s="1"/>
       <c r="M106" s="12"/>
       <c r="S106" s="12"/>
     </row>
-    <row r="107" spans="1:26" s="1" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D107" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E107" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F107" s="29" t="s">
-        <v>401</v>
+    <row r="107" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D107" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E107" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" s="35" t="s">
+        <v>209</v>
       </c>
       <c r="G107" s="12"/>
+      <c r="H107" s="1"/>
       <c r="M107" s="12"/>
       <c r="S107" s="12"/>
-      <c r="Y107" s="22" t="s">
-        <v>397</v>
-      </c>
-      <c r="Z107" s="12" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="108" spans="1:26" s="1" customFormat="1" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A108" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="B108" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C108" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="D108" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E108" s="22" t="b">
+    </row>
+    <row r="108" spans="1:26" s="1" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D108" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E108" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F108" s="29" t="s">
-        <v>16</v>
+        <v>401</v>
       </c>
       <c r="G108" s="12"/>
       <c r="M108" s="12"/>
       <c r="S108" s="12"/>
       <c r="Y108" s="22" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="Z108" s="12" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="109" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A109" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B109" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26" s="1" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A109" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="B109" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D109" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E109" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>4</v>
+      <c r="C109" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="D109" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" s="29" t="s">
+        <v>16</v>
       </c>
       <c r="G109" s="12"/>
       <c r="M109" s="12"/>
       <c r="S109" s="12"/>
-    </row>
-    <row r="110" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="Y109" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="Z109" s="12" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="D110" s="1" t="b">
         <v>0</v>
@@ -5169,44 +5175,44 @@
         <v>1</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G110" s="12"/>
       <c r="M110" s="12"/>
       <c r="S110" s="12"/>
     </row>
-    <row r="111" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>106</v>
+        <v>199</v>
       </c>
       <c r="D111" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="G111" s="12"/>
       <c r="M111" s="12"/>
       <c r="S111" s="12"/>
     </row>
-    <row r="112" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D112" s="1" t="b">
         <v>1</v>
@@ -5215,56 +5221,44 @@
         <v>0</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>399</v>
+        <v>104</v>
       </c>
       <c r="G112" s="12"/>
       <c r="M112" s="12"/>
       <c r="S112" s="12"/>
     </row>
-    <row r="113" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A113" s="4" t="s">
+    <row r="113" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D113" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="G113" s="12"/>
+      <c r="M113" s="12"/>
+      <c r="S113" s="12"/>
+    </row>
+    <row r="114" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A114" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B114" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C114" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="D113" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E113" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F113" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="G113" s="12"/>
-      <c r="H113" s="1"/>
-      <c r="M113" s="12"/>
-      <c r="N113" s="1"/>
-      <c r="O113" s="1"/>
-      <c r="R113" s="1"/>
-      <c r="S113" s="12"/>
-      <c r="U113" s="1"/>
-      <c r="X113" s="1"/>
-      <c r="Y113" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="Z113" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="114" spans="1:26" s="4" customFormat="1" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A114" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="D114" s="4" t="b">
         <v>1</v>
@@ -5278,126 +5272,102 @@
       <c r="G114" s="12"/>
       <c r="H114" s="1"/>
       <c r="M114" s="12"/>
+      <c r="N114" s="1"/>
+      <c r="O114" s="1"/>
+      <c r="R114" s="1"/>
       <c r="S114" s="12"/>
+      <c r="U114" s="1"/>
+      <c r="X114" s="1"/>
       <c r="Y114" s="21" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="Z114" s="4" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="115" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A115" t="s">
-        <v>113</v>
-      </c>
-      <c r="B115" t="s">
-        <v>5</v>
-      </c>
-      <c r="C115" t="s">
-        <v>114</v>
-      </c>
-      <c r="D115" t="b">
-        <v>1</v>
-      </c>
-      <c r="E115" t="b">
-        <v>1</v>
-      </c>
-      <c r="F115" s="28" t="s">
-        <v>16</v>
+    <row r="115" spans="1:26" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A115" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D115" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E115" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" s="27" t="s">
+        <v>209</v>
       </c>
       <c r="G115" s="12"/>
       <c r="H115" s="1"/>
       <c r="M115" s="12"/>
-      <c r="N115" s="1"/>
-      <c r="O115" s="1"/>
-      <c r="R115" s="1"/>
       <c r="S115" s="12"/>
       <c r="Y115" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="Z115" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>113</v>
+      </c>
+      <c r="B116" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116" t="s">
+        <v>114</v>
+      </c>
+      <c r="D116" t="b">
+        <v>1</v>
+      </c>
+      <c r="E116" t="b">
+        <v>1</v>
+      </c>
+      <c r="F116" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" s="12"/>
+      <c r="H116" s="1"/>
+      <c r="M116" s="12"/>
+      <c r="N116" s="1"/>
+      <c r="O116" s="1"/>
+      <c r="R116" s="1"/>
+      <c r="S116" s="12"/>
+      <c r="Y116" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="Z115" s="4" t="s">
+      <c r="Z116" s="4" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="116" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="1" t="s">
+    <row r="117" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C117" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D116" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E116" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F116" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="G116" s="12"/>
-      <c r="I116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M116" s="12"/>
-      <c r="O116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="P116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="R116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S116" s="12"/>
-      <c r="U116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="V116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="W116" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="X116" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A117" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="B117" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C117" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="D117" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E117" s="32" t="b">
+      <c r="D117" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E117" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F117" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G117" s="24"/>
+      <c r="G117" s="12"/>
       <c r="I117" s="1" t="s">
         <v>4</v>
       </c>
@@ -5437,18 +5407,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B118" s="32" t="s">
         <v>5</v>
       </c>
       <c r="C118" s="32" t="s">
-        <v>119</v>
+        <v>316</v>
       </c>
       <c r="D118" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" s="32" t="b">
         <v>1</v>
@@ -5457,6 +5427,18 @@
         <v>16</v>
       </c>
       <c r="G118" s="24"/>
+      <c r="I118" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="M118" s="12"/>
       <c r="O118" s="1" t="s">
         <v>4</v>
@@ -5484,196 +5466,184 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A119" s="4" t="s">
+    <row r="119" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B119" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="D119" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E119" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F119" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" s="24"/>
+      <c r="M119" s="12"/>
+      <c r="O119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S119" s="12"/>
+      <c r="U119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W119" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X119" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A120" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B120" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C120" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D119" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E119" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F119" s="27"/>
-      <c r="G119" s="24"/>
-      <c r="I119"/>
-      <c r="J119"/>
-      <c r="K119"/>
-      <c r="L119"/>
-      <c r="M119" s="12"/>
-      <c r="S119" s="12"/>
-    </row>
-    <row r="120" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D120" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E120" s="5" t="b">
+      <c r="D120" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120" s="4" t="b">
         <v>1</v>
       </c>
       <c r="F120" s="27"/>
       <c r="G120" s="24"/>
-      <c r="H120" s="1"/>
       <c r="I120"/>
       <c r="J120"/>
       <c r="K120"/>
       <c r="L120"/>
       <c r="M120" s="12"/>
-      <c r="N120"/>
-      <c r="O120"/>
-      <c r="P120"/>
-      <c r="Q120"/>
-      <c r="R120"/>
       <c r="S120" s="12"/>
-      <c r="T120"/>
-      <c r="U120"/>
-      <c r="V120"/>
-      <c r="W120"/>
-      <c r="X120"/>
-    </row>
-    <row r="121" spans="1:26" s="4" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
-      <c r="A121" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B121" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C121" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D121" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E121" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F121" s="28" t="s">
-        <v>19</v>
-      </c>
+    </row>
+    <row r="121" spans="1:26" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D121" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E121" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F121" s="27"/>
       <c r="G121" s="24"/>
       <c r="H121" s="1"/>
-      <c r="I121" s="1" t="s">
+      <c r="I121"/>
+      <c r="J121"/>
+      <c r="K121"/>
+      <c r="L121"/>
+      <c r="M121" s="12"/>
+      <c r="N121"/>
+      <c r="O121"/>
+      <c r="P121"/>
+      <c r="Q121"/>
+      <c r="R121"/>
+      <c r="S121" s="12"/>
+      <c r="T121"/>
+      <c r="U121"/>
+      <c r="V121"/>
+      <c r="W121"/>
+      <c r="X121"/>
+    </row>
+    <row r="122" spans="1:26" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A122" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B122" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C122" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D122" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E122" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F122" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G122" s="24"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="J121" s="1" t="s">
+      <c r="J122" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="K121" s="1" t="s">
+      <c r="K122" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="L121" s="1" t="s">
+      <c r="L122" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="M121" s="12"/>
-      <c r="N121" s="1"/>
-      <c r="O121" s="1" t="s">
+      <c r="M122" s="12"/>
+      <c r="N122" s="1"/>
+      <c r="O122" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="P121" s="1" t="s">
+      <c r="P122" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="Q121" s="1" t="s">
+      <c r="Q122" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="R121" s="1" t="s">
+      <c r="R122" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="S121" s="12"/>
-      <c r="U121" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="V121" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="W121" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="X121" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="122" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="B122" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="D122" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E122" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F122" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G122" s="12"/>
-      <c r="I122" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M122" s="12"/>
-      <c r="O122" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="P122" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q122" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="R122" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="S122" s="12"/>
       <c r="U122" s="1" t="s">
-        <v>4</v>
+        <v>351</v>
       </c>
       <c r="V122" s="1" t="s">
-        <v>4</v>
+        <v>351</v>
       </c>
       <c r="W122" s="1" t="s">
-        <v>4</v>
+        <v>351</v>
       </c>
       <c r="X122" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="123" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="32" t="s">
-        <v>229</v>
+        <v>123</v>
       </c>
       <c r="B123" s="32" t="s">
         <v>5</v>
       </c>
       <c r="C123" s="32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D123" s="32" t="b">
         <v>1</v>
@@ -5681,10 +5651,10 @@
       <c r="E123" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="F123" s="34" t="s">
+      <c r="F123" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="G123" s="24"/>
+      <c r="G123" s="12"/>
       <c r="I123" s="1" t="s">
         <v>4</v>
       </c>
@@ -5724,120 +5694,167 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="B124" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="D124" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E124" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F124" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" s="24"/>
+      <c r="I124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="M124" s="12"/>
+      <c r="O124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="R124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="S124" s="12"/>
+      <c r="U124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W124" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X124" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="B124" s="32" t="s">
+      <c r="B125" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C124" s="32" t="s">
+      <c r="C125" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="D124" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E124" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F124" s="26" t="s">
+      <c r="D125" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="G124" s="24"/>
-      <c r="M124" s="12"/>
-      <c r="S124" s="12"/>
-    </row>
-    <row r="125" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="D125" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E125" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G125" s="12"/>
+      <c r="G125" s="24"/>
       <c r="M125" s="12"/>
       <c r="S125" s="12"/>
     </row>
-    <row r="126" spans="1:26" s="1" customFormat="1" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A126" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="B126" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="C126" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="D126" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E126" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F126" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="G126" s="24"/>
+    <row r="126" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D126" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E126" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G126" s="12"/>
       <c r="M126" s="12"/>
       <c r="S126" s="12"/>
-      <c r="Y126" s="22" t="s">
-        <v>343</v>
-      </c>
-      <c r="Z126" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="127" spans="1:26" s="1" customFormat="1" ht="29.15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="127" spans="1:26" s="1" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A127" s="32" t="s">
-        <v>128</v>
+        <v>244</v>
       </c>
       <c r="B127" s="32" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="C127" s="32" t="s">
-        <v>130</v>
+        <v>245</v>
       </c>
       <c r="D127" s="32" t="b">
         <v>1</v>
       </c>
       <c r="E127" s="32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="G127" s="24"/>
       <c r="M127" s="12"/>
       <c r="S127" s="12"/>
       <c r="Y127" s="22" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="Z127" s="1" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A128" s="20"/>
-      <c r="B128" s="20"/>
-      <c r="C128" s="20"/>
-      <c r="D128" s="20"/>
-      <c r="E128" s="20"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="25"/>
-      <c r="H128" s="19"/>
-      <c r="N128" s="1"/>
+    <row r="128" spans="1:26" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A128" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="C128" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D128" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E128" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="G128" s="24"/>
+      <c r="M128" s="12"/>
       <c r="S128" s="12"/>
-    </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.4">
+      <c r="Y128" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="Z128" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129" s="20"/>
       <c r="B129" s="20"/>
       <c r="C129" s="20"/>
@@ -5846,9 +5863,10 @@
       <c r="F129" s="20"/>
       <c r="G129" s="25"/>
       <c r="H129" s="19"/>
+      <c r="N129" s="1"/>
       <c r="S129" s="12"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130" s="20"/>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
@@ -5859,7 +5877,7 @@
       <c r="H130" s="19"/>
       <c r="S130" s="12"/>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131" s="20"/>
       <c r="B131" s="20"/>
       <c r="C131" s="20"/>
@@ -5870,7 +5888,7 @@
       <c r="H131" s="19"/>
       <c r="S131" s="12"/>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132" s="20"/>
       <c r="B132" s="20"/>
       <c r="C132" s="20"/>
@@ -5881,7 +5899,7 @@
       <c r="H132" s="19"/>
       <c r="S132" s="12"/>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133" s="20"/>
       <c r="B133" s="20"/>
       <c r="C133" s="20"/>
@@ -5892,7 +5910,7 @@
       <c r="H133" s="19"/>
       <c r="S133" s="12"/>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134" s="20"/>
       <c r="B134" s="20"/>
       <c r="C134" s="20"/>
@@ -5903,7 +5921,7 @@
       <c r="H134" s="19"/>
       <c r="S134" s="12"/>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135" s="20"/>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -5914,7 +5932,7 @@
       <c r="H135" s="19"/>
       <c r="S135" s="12"/>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136" s="20"/>
       <c r="B136" s="20"/>
       <c r="C136" s="20"/>
@@ -5925,7 +5943,7 @@
       <c r="H136" s="19"/>
       <c r="S136" s="12"/>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137" s="20"/>
       <c r="B137" s="20"/>
       <c r="C137" s="20"/>
@@ -5933,9 +5951,10 @@
       <c r="E137" s="20"/>
       <c r="F137" s="20"/>
       <c r="G137" s="25"/>
+      <c r="H137" s="19"/>
       <c r="S137" s="12"/>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138" s="20"/>
       <c r="B138" s="20"/>
       <c r="C138" s="20"/>
@@ -5945,7 +5964,7 @@
       <c r="G138" s="25"/>
       <c r="S138" s="12"/>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139" s="20"/>
       <c r="B139" s="20"/>
       <c r="C139" s="20"/>
@@ -5955,7 +5974,7 @@
       <c r="G139" s="25"/>
       <c r="S139" s="12"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140" s="20"/>
       <c r="B140" s="20"/>
       <c r="C140" s="20"/>
@@ -5965,7 +5984,7 @@
       <c r="G140" s="25"/>
       <c r="S140" s="12"/>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141" s="20"/>
       <c r="B141" s="20"/>
       <c r="C141" s="20"/>
@@ -5975,7 +5994,7 @@
       <c r="G141" s="25"/>
       <c r="S141" s="12"/>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142" s="20"/>
       <c r="B142" s="20"/>
       <c r="C142" s="20"/>
@@ -5985,7 +6004,7 @@
       <c r="G142" s="25"/>
       <c r="S142" s="12"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143" s="20"/>
       <c r="B143" s="20"/>
       <c r="C143" s="20"/>
@@ -5995,7 +6014,7 @@
       <c r="G143" s="25"/>
       <c r="S143" s="12"/>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144" s="20"/>
       <c r="B144" s="20"/>
       <c r="C144" s="20"/>
@@ -6005,7 +6024,7 @@
       <c r="G144" s="25"/>
       <c r="S144" s="12"/>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A145" s="20"/>
       <c r="B145" s="20"/>
       <c r="C145" s="20"/>
@@ -6015,7 +6034,7 @@
       <c r="G145" s="25"/>
       <c r="S145" s="12"/>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A146" s="20"/>
       <c r="B146" s="20"/>
       <c r="C146" s="20"/>
@@ -6025,7 +6044,7 @@
       <c r="G146" s="25"/>
       <c r="S146" s="12"/>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A147" s="20"/>
       <c r="B147" s="20"/>
       <c r="C147" s="20"/>
@@ -6035,7 +6054,7 @@
       <c r="G147" s="25"/>
       <c r="S147" s="12"/>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A148" s="20"/>
       <c r="B148" s="20"/>
       <c r="C148" s="20"/>
@@ -6045,7 +6064,7 @@
       <c r="G148" s="25"/>
       <c r="S148" s="12"/>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A149" s="20"/>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -6055,7 +6074,7 @@
       <c r="G149" s="25"/>
       <c r="S149" s="12"/>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A150" s="20"/>
       <c r="B150" s="20"/>
       <c r="C150" s="20"/>
@@ -6065,7 +6084,7 @@
       <c r="G150" s="25"/>
       <c r="S150" s="12"/>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A151" s="20"/>
       <c r="B151" s="20"/>
       <c r="C151" s="20"/>
@@ -6075,7 +6094,7 @@
       <c r="G151" s="25"/>
       <c r="S151" s="12"/>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A152" s="20"/>
       <c r="B152" s="20"/>
       <c r="C152" s="20"/>
@@ -6085,7 +6104,7 @@
       <c r="G152" s="25"/>
       <c r="S152" s="12"/>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A153" s="20"/>
       <c r="B153" s="20"/>
       <c r="C153" s="20"/>
@@ -6095,7 +6114,7 @@
       <c r="G153" s="25"/>
       <c r="S153" s="12"/>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A154" s="20"/>
       <c r="B154" s="20"/>
       <c r="C154" s="20"/>
@@ -6105,7 +6124,7 @@
       <c r="G154" s="25"/>
       <c r="S154" s="12"/>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A155" s="20"/>
       <c r="B155" s="20"/>
       <c r="C155" s="20"/>
@@ -6115,7 +6134,7 @@
       <c r="G155" s="25"/>
       <c r="S155" s="12"/>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A156" s="20"/>
       <c r="B156" s="20"/>
       <c r="C156" s="20"/>
@@ -6125,7 +6144,7 @@
       <c r="G156" s="25"/>
       <c r="S156" s="12"/>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A157" s="20"/>
       <c r="B157" s="20"/>
       <c r="C157" s="20"/>
@@ -6135,7 +6154,7 @@
       <c r="G157" s="25"/>
       <c r="S157" s="12"/>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A158" s="20"/>
       <c r="B158" s="20"/>
       <c r="C158" s="20"/>
@@ -6143,19 +6162,29 @@
       <c r="E158" s="20"/>
       <c r="F158" s="20"/>
       <c r="G158" s="25"/>
+      <c r="S158" s="12"/>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A159" s="20"/>
+      <c r="B159" s="20"/>
+      <c r="C159" s="20"/>
+      <c r="D159" s="20"/>
+      <c r="E159" s="20"/>
+      <c r="F159" s="20"/>
+      <c r="G159" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="Y45:Y46"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
     <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="Y45:Y46"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
@@ -6170,18 +6199,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.69140625" customWidth="1"/>
-    <col min="2" max="2" width="52.23046875" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>226</v>
       </c>
@@ -6189,7 +6218,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>227</v>
       </c>
@@ -6197,8 +6226,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="6" spans="1:2" ht="19.3" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="1:2" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="3" t="s">
         <v>205</v>
       </c>
@@ -6206,7 +6235,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="19.3" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>206</v>
       </c>
@@ -6214,7 +6243,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="19.3" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
         <v>207</v>
       </c>
@@ -6222,7 +6251,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:2" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/input/KING/props/KING.xlsx
+++ b/src/main/resources/input/KING/props/KING.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\github.com\Imvertor-Maven\src\main\resources\input\KING\props\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB5AC0F-B5C4-4D0A-83FD-81B31C20F5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C26B49E-64D6-4FAF-8B42-D6755A1C9399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5610" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
